--- a/Chaos_Experiment_Review_Tracker.xlsx
+++ b/Chaos_Experiment_Review_Tracker.xlsx
@@ -9,8 +9,15 @@
   </bookViews>
   <sheets>
     <sheet name="Review Tracker" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="How to Use" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Lists" sheetId="2" state="hidden" r:id="rId4"/>
+    <sheet name="How to Use" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="false" name="FaultTypeList" vbProcedure="false">Lists!$A$2:$A$16</definedName>
+    <definedName function="false" hidden="false" name="NotesPhraseList" vbProcedure="false">Lists!$D$2:$D$11</definedName>
+    <definedName function="false" hidden="false" name="ReviewerList" vbProcedure="false">Lists!$C$2:$C$6</definedName>
+    <definedName function="false" hidden="false" name="YesPartialNoList" vbProcedure="false">Lists!$B$2:$B$4</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -21,12 +28,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
   <si>
     <t xml:space="preserve">Chaos Testing Experiment Review Tracker</t>
   </si>
   <si>
-    <t xml:space="preserve">Fast-pass review filter — 4 key gap checks per experiment. Answer Yes / Partial / No from each column's dropdown.</t>
+    <t xml:space="preserve">Fast-pass review filter — pick from dropdowns in every column, no free typing needed for standard fields.</t>
   </si>
   <si>
     <t xml:space="preserve">No.</t>
@@ -77,43 +84,160 @@
     <t xml:space="preserve">Major Gaps (Send Back)</t>
   </si>
   <si>
+    <t xml:space="preserve">FaultTypes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YesPartialNo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reviewers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NotesPhrases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pod Kill / Termination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Self</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No steady-state baseline documented</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Node Failure / Drain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peer Reviewer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verdict not backed by dashboard/query link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Latency Injection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No rollback/abort criteria defined</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Packet Loss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copilot verdict doesn't match stated hypothesis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Partition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blast radius not clearly scoped</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNS Chaos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No stakeholder sign-off recorded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPU Stress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTTR/recovery time not captured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Memory Stress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Looks solid - no major gaps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disk I/O Latency/Fault</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs re-run with proper evidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Container Kill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escalate - customer-facing risk unclear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubelet/API Server Failure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clock Skew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dependency/Service Failure (downstream)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Database Connection Failure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other</t>
+  </si>
+  <si>
     <t xml:space="preserve">Purpose</t>
   </si>
   <si>
     <t xml:space="preserve">A fast filter to review all 25 chaos experiments against 4 common gaps, without deep-diving each one.</t>
   </si>
   <si>
+    <t xml:space="preserve">Every dropdown column is pre-populated with standard items</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Fault Type (col C): standard chaos engineering fault categories (pod kill, network chaos, resource stress, etc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Columns D-G: Yes / Partial / No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Reviewer Notes (col J): common standard gap phrases - pick one or type your own freely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Reviewed By (col K): standard reviewer role list</t>
+  </si>
+  <si>
     <t xml:space="preserve">How to fill it in</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Paste the experiment name and a link to its Confluence section in column B.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. For each of the 4 questions (columns D-G), select Yes / Partial / No from the dropdown based on what's actually documented.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - Yes = evidence clearly present (linked dashboard, defined baseline, etc.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - Partial = mentioned in text but no supporting data/link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - No = missing entirely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Gap Score and Review Status calculate automatically:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - 0 points = Pass, no gaps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - 1-2 points = Minor gaps (note them, can proceed with follow-up)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - 3+ points = Major gaps (send back before accepting the verdict)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Use Reviewer Notes for anything specific worth flagging (e.g. 'Copilot verdict says pass but no error-rate data shown').</t>
+    <t xml:space="preserve">1. Paste the experiment name and Confluence link in column B.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Select the Fault Type from the dropdown in column C.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. For each of the 4 gap questions (D-G), select Yes / Partial / No based on what's actually documented.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Yes = evidence clearly present. Partial = mentioned but no supporting link/data. No = missing entirely.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Gap Score and Review Status calculate automatically:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   0 points = Pass, no gaps | 1-2 points = Minor gaps | 3+ points = Major gaps, send back</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Pick a standard note from column J's dropdown, or type a custom one - the cell still accepts free text.</t>
   </si>
   <si>
     <t xml:space="preserve">The 4 questions</t>
@@ -125,10 +249,10 @@
     <t xml:space="preserve">2. Evidence Linked? - Is there an actual Dynatrace/CloudWatch link or screenshot behind the verdict, not just prose?</t>
   </si>
   <si>
-    <t xml:space="preserve">3. Rollback/Abort Criteria Defined? - Was there a defined stop condition or rollback plan, not just 'we ran it and watched'?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Verdict Matches Hypothesis? - Does the stated conclusion actually answer the original hypothesis, or is it a generic 'system handled it well'?</t>
+    <t xml:space="preserve">3. Rollback/Abort Criteria Defined? - Was there a defined stop condition or rollback plan?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Verdict Matches Hypothesis? - Does the stated conclusion actually answer the original hypothesis?</t>
   </si>
 </sst>
 </file>
@@ -578,15 +702,14 @@
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -669,7 +792,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="6" t="str">
-        <f aca="false">IF(COUNTBLANK(D5:G5)=4,"Not Reviewed",IF(H5=0,"✅ Pass - No Gaps",IF(H5&lt;=2,"⚠ Minor Gaps","❌ Major Gaps - Send Back")))</f>
+        <f aca="false">IF(COUNTBLANK(D5:G5)=4,"Not Reviewed",IF(H5=0,"Pass - No Gaps",IF(H5&lt;=2,"Minor Gaps","Major Gaps - Send Back")))</f>
         <v>Not Reviewed</v>
       </c>
       <c r="J5" s="5"/>
@@ -690,7 +813,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="6" t="str">
-        <f aca="false">IF(COUNTBLANK(D6:G6)=4,"Not Reviewed",IF(H6=0,"✅ Pass - No Gaps",IF(H6&lt;=2,"⚠ Minor Gaps","❌ Major Gaps - Send Back")))</f>
+        <f aca="false">IF(COUNTBLANK(D6:G6)=4,"Not Reviewed",IF(H6=0,"Pass - No Gaps",IF(H6&lt;=2,"Minor Gaps","Major Gaps - Send Back")))</f>
         <v>Not Reviewed</v>
       </c>
       <c r="J6" s="5"/>
@@ -711,7 +834,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="6" t="str">
-        <f aca="false">IF(COUNTBLANK(D7:G7)=4,"Not Reviewed",IF(H7=0,"✅ Pass - No Gaps",IF(H7&lt;=2,"⚠ Minor Gaps","❌ Major Gaps - Send Back")))</f>
+        <f aca="false">IF(COUNTBLANK(D7:G7)=4,"Not Reviewed",IF(H7=0,"Pass - No Gaps",IF(H7&lt;=2,"Minor Gaps","Major Gaps - Send Back")))</f>
         <v>Not Reviewed</v>
       </c>
       <c r="J7" s="5"/>
@@ -732,7 +855,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="6" t="str">
-        <f aca="false">IF(COUNTBLANK(D8:G8)=4,"Not Reviewed",IF(H8=0,"✅ Pass - No Gaps",IF(H8&lt;=2,"⚠ Minor Gaps","❌ Major Gaps - Send Back")))</f>
+        <f aca="false">IF(COUNTBLANK(D8:G8)=4,"Not Reviewed",IF(H8=0,"Pass - No Gaps",IF(H8&lt;=2,"Minor Gaps","Major Gaps - Send Back")))</f>
         <v>Not Reviewed</v>
       </c>
       <c r="J8" s="5"/>
@@ -753,7 +876,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="6" t="str">
-        <f aca="false">IF(COUNTBLANK(D9:G9)=4,"Not Reviewed",IF(H9=0,"✅ Pass - No Gaps",IF(H9&lt;=2,"⚠ Minor Gaps","❌ Major Gaps - Send Back")))</f>
+        <f aca="false">IF(COUNTBLANK(D9:G9)=4,"Not Reviewed",IF(H9=0,"Pass - No Gaps",IF(H9&lt;=2,"Minor Gaps","Major Gaps - Send Back")))</f>
         <v>Not Reviewed</v>
       </c>
       <c r="J9" s="5"/>
@@ -774,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="6" t="str">
-        <f aca="false">IF(COUNTBLANK(D10:G10)=4,"Not Reviewed",IF(H10=0,"✅ Pass - No Gaps",IF(H10&lt;=2,"⚠ Minor Gaps","❌ Major Gaps - Send Back")))</f>
+        <f aca="false">IF(COUNTBLANK(D10:G10)=4,"Not Reviewed",IF(H10=0,"Pass - No Gaps",IF(H10&lt;=2,"Minor Gaps","Major Gaps - Send Back")))</f>
         <v>Not Reviewed</v>
       </c>
       <c r="J10" s="5"/>
@@ -795,7 +918,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="6" t="str">
-        <f aca="false">IF(COUNTBLANK(D11:G11)=4,"Not Reviewed",IF(H11=0,"✅ Pass - No Gaps",IF(H11&lt;=2,"⚠ Minor Gaps","❌ Major Gaps - Send Back")))</f>
+        <f aca="false">IF(COUNTBLANK(D11:G11)=4,"Not Reviewed",IF(H11=0,"Pass - No Gaps",IF(H11&lt;=2,"Minor Gaps","Major Gaps - Send Back")))</f>
         <v>Not Reviewed</v>
       </c>
       <c r="J11" s="5"/>
@@ -816,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="6" t="str">
-        <f aca="false">IF(COUNTBLANK(D12:G12)=4,"Not Reviewed",IF(H12=0,"✅ Pass - No Gaps",IF(H12&lt;=2,"⚠ Minor Gaps","❌ Major Gaps - Send Back")))</f>
+        <f aca="false">IF(COUNTBLANK(D12:G12)=4,"Not Reviewed",IF(H12=0,"Pass - No Gaps",IF(H12&lt;=2,"Minor Gaps","Major Gaps - Send Back")))</f>
         <v>Not Reviewed</v>
       </c>
       <c r="J12" s="5"/>
@@ -837,7 +960,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="6" t="str">
-        <f aca="false">IF(COUNTBLANK(D13:G13)=4,"Not Reviewed",IF(H13=0,"✅ Pass - No Gaps",IF(H13&lt;=2,"⚠ Minor Gaps","❌ Major Gaps - Send Back")))</f>
+        <f aca="false">IF(COUNTBLANK(D13:G13)=4,"Not Reviewed",IF(H13=0,"Pass - No Gaps",IF(H13&lt;=2,"Minor Gaps","Major Gaps - Send Back")))</f>
         <v>Not Reviewed</v>
       </c>
       <c r="J13" s="5"/>
@@ -858,7 +981,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="6" t="str">
-        <f aca="false">IF(COUNTBLANK(D14:G14)=4,"Not Reviewed",IF(H14=0,"✅ Pass - No Gaps",IF(H14&lt;=2,"⚠ Minor Gaps","❌ Major Gaps - Send Back")))</f>
+        <f aca="false">IF(COUNTBLANK(D14:G14)=4,"Not Reviewed",IF(H14=0,"Pass - No Gaps",IF(H14&lt;=2,"Minor Gaps","Major Gaps - Send Back")))</f>
         <v>Not Reviewed</v>
       </c>
       <c r="J14" s="5"/>
@@ -879,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="6" t="str">
-        <f aca="false">IF(COUNTBLANK(D15:G15)=4,"Not Reviewed",IF(H15=0,"✅ Pass - No Gaps",IF(H15&lt;=2,"⚠ Minor Gaps","❌ Major Gaps - Send Back")))</f>
+        <f aca="false">IF(COUNTBLANK(D15:G15)=4,"Not Reviewed",IF(H15=0,"Pass - No Gaps",IF(H15&lt;=2,"Minor Gaps","Major Gaps - Send Back")))</f>
         <v>Not Reviewed</v>
       </c>
       <c r="J15" s="5"/>
@@ -900,7 +1023,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="6" t="str">
-        <f aca="false">IF(COUNTBLANK(D16:G16)=4,"Not Reviewed",IF(H16=0,"✅ Pass - No Gaps",IF(H16&lt;=2,"⚠ Minor Gaps","❌ Major Gaps - Send Back")))</f>
+        <f aca="false">IF(COUNTBLANK(D16:G16)=4,"Not Reviewed",IF(H16=0,"Pass - No Gaps",IF(H16&lt;=2,"Minor Gaps","Major Gaps - Send Back")))</f>
         <v>Not Reviewed</v>
       </c>
       <c r="J16" s="5"/>
@@ -921,7 +1044,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="6" t="str">
-        <f aca="false">IF(COUNTBLANK(D17:G17)=4,"Not Reviewed",IF(H17=0,"✅ Pass - No Gaps",IF(H17&lt;=2,"⚠ Minor Gaps","❌ Major Gaps - Send Back")))</f>
+        <f aca="false">IF(COUNTBLANK(D17:G17)=4,"Not Reviewed",IF(H17=0,"Pass - No Gaps",IF(H17&lt;=2,"Minor Gaps","Major Gaps - Send Back")))</f>
         <v>Not Reviewed</v>
       </c>
       <c r="J17" s="5"/>
@@ -942,7 +1065,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="6" t="str">
-        <f aca="false">IF(COUNTBLANK(D18:G18)=4,"Not Reviewed",IF(H18=0,"✅ Pass - No Gaps",IF(H18&lt;=2,"⚠ Minor Gaps","❌ Major Gaps - Send Back")))</f>
+        <f aca="false">IF(COUNTBLANK(D18:G18)=4,"Not Reviewed",IF(H18=0,"Pass - No Gaps",IF(H18&lt;=2,"Minor Gaps","Major Gaps - Send Back")))</f>
         <v>Not Reviewed</v>
       </c>
       <c r="J18" s="5"/>
@@ -963,7 +1086,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="6" t="str">
-        <f aca="false">IF(COUNTBLANK(D19:G19)=4,"Not Reviewed",IF(H19=0,"✅ Pass - No Gaps",IF(H19&lt;=2,"⚠ Minor Gaps","❌ Major Gaps - Send Back")))</f>
+        <f aca="false">IF(COUNTBLANK(D19:G19)=4,"Not Reviewed",IF(H19=0,"Pass - No Gaps",IF(H19&lt;=2,"Minor Gaps","Major Gaps - Send Back")))</f>
         <v>Not Reviewed</v>
       </c>
       <c r="J19" s="5"/>
@@ -984,7 +1107,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="6" t="str">
-        <f aca="false">IF(COUNTBLANK(D20:G20)=4,"Not Reviewed",IF(H20=0,"✅ Pass - No Gaps",IF(H20&lt;=2,"⚠ Minor Gaps","❌ Major Gaps - Send Back")))</f>
+        <f aca="false">IF(COUNTBLANK(D20:G20)=4,"Not Reviewed",IF(H20=0,"Pass - No Gaps",IF(H20&lt;=2,"Minor Gaps","Major Gaps - Send Back")))</f>
         <v>Not Reviewed</v>
       </c>
       <c r="J20" s="5"/>
@@ -1005,7 +1128,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="6" t="str">
-        <f aca="false">IF(COUNTBLANK(D21:G21)=4,"Not Reviewed",IF(H21=0,"✅ Pass - No Gaps",IF(H21&lt;=2,"⚠ Minor Gaps","❌ Major Gaps - Send Back")))</f>
+        <f aca="false">IF(COUNTBLANK(D21:G21)=4,"Not Reviewed",IF(H21=0,"Pass - No Gaps",IF(H21&lt;=2,"Minor Gaps","Major Gaps - Send Back")))</f>
         <v>Not Reviewed</v>
       </c>
       <c r="J21" s="5"/>
@@ -1026,7 +1149,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="6" t="str">
-        <f aca="false">IF(COUNTBLANK(D22:G22)=4,"Not Reviewed",IF(H22=0,"✅ Pass - No Gaps",IF(H22&lt;=2,"⚠ Minor Gaps","❌ Major Gaps - Send Back")))</f>
+        <f aca="false">IF(COUNTBLANK(D22:G22)=4,"Not Reviewed",IF(H22=0,"Pass - No Gaps",IF(H22&lt;=2,"Minor Gaps","Major Gaps - Send Back")))</f>
         <v>Not Reviewed</v>
       </c>
       <c r="J22" s="5"/>
@@ -1047,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="6" t="str">
-        <f aca="false">IF(COUNTBLANK(D23:G23)=4,"Not Reviewed",IF(H23=0,"✅ Pass - No Gaps",IF(H23&lt;=2,"⚠ Minor Gaps","❌ Major Gaps - Send Back")))</f>
+        <f aca="false">IF(COUNTBLANK(D23:G23)=4,"Not Reviewed",IF(H23=0,"Pass - No Gaps",IF(H23&lt;=2,"Minor Gaps","Major Gaps - Send Back")))</f>
         <v>Not Reviewed</v>
       </c>
       <c r="J23" s="5"/>
@@ -1068,7 +1191,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="6" t="str">
-        <f aca="false">IF(COUNTBLANK(D24:G24)=4,"Not Reviewed",IF(H24=0,"✅ Pass - No Gaps",IF(H24&lt;=2,"⚠ Minor Gaps","❌ Major Gaps - Send Back")))</f>
+        <f aca="false">IF(COUNTBLANK(D24:G24)=4,"Not Reviewed",IF(H24=0,"Pass - No Gaps",IF(H24&lt;=2,"Minor Gaps","Major Gaps - Send Back")))</f>
         <v>Not Reviewed</v>
       </c>
       <c r="J24" s="5"/>
@@ -1089,7 +1212,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="6" t="str">
-        <f aca="false">IF(COUNTBLANK(D25:G25)=4,"Not Reviewed",IF(H25=0,"✅ Pass - No Gaps",IF(H25&lt;=2,"⚠ Minor Gaps","❌ Major Gaps - Send Back")))</f>
+        <f aca="false">IF(COUNTBLANK(D25:G25)=4,"Not Reviewed",IF(H25=0,"Pass - No Gaps",IF(H25&lt;=2,"Minor Gaps","Major Gaps - Send Back")))</f>
         <v>Not Reviewed</v>
       </c>
       <c r="J25" s="5"/>
@@ -1110,7 +1233,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="6" t="str">
-        <f aca="false">IF(COUNTBLANK(D26:G26)=4,"Not Reviewed",IF(H26=0,"✅ Pass - No Gaps",IF(H26&lt;=2,"⚠ Minor Gaps","❌ Major Gaps - Send Back")))</f>
+        <f aca="false">IF(COUNTBLANK(D26:G26)=4,"Not Reviewed",IF(H26=0,"Pass - No Gaps",IF(H26&lt;=2,"Minor Gaps","Major Gaps - Send Back")))</f>
         <v>Not Reviewed</v>
       </c>
       <c r="J26" s="5"/>
@@ -1131,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="6" t="str">
-        <f aca="false">IF(COUNTBLANK(D27:G27)=4,"Not Reviewed",IF(H27=0,"✅ Pass - No Gaps",IF(H27&lt;=2,"⚠ Minor Gaps","❌ Major Gaps - Send Back")))</f>
+        <f aca="false">IF(COUNTBLANK(D27:G27)=4,"Not Reviewed",IF(H27=0,"Pass - No Gaps",IF(H27&lt;=2,"Minor Gaps","Major Gaps - Send Back")))</f>
         <v>Not Reviewed</v>
       </c>
       <c r="J27" s="5"/>
@@ -1152,7 +1275,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="6" t="str">
-        <f aca="false">IF(COUNTBLANK(D28:G28)=4,"Not Reviewed",IF(H28=0,"✅ Pass - No Gaps",IF(H28&lt;=2,"⚠ Minor Gaps","❌ Major Gaps - Send Back")))</f>
+        <f aca="false">IF(COUNTBLANK(D28:G28)=4,"Not Reviewed",IF(H28=0,"Pass - No Gaps",IF(H28&lt;=2,"Minor Gaps","Major Gaps - Send Back")))</f>
         <v>Not Reviewed</v>
       </c>
       <c r="J28" s="5"/>
@@ -1173,7 +1296,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="6" t="str">
-        <f aca="false">IF(COUNTBLANK(D29:G29)=4,"Not Reviewed",IF(H29=0,"✅ Pass - No Gaps",IF(H29&lt;=2,"⚠ Minor Gaps","❌ Major Gaps - Send Back")))</f>
+        <f aca="false">IF(COUNTBLANK(D29:G29)=4,"Not Reviewed",IF(H29=0,"Pass - No Gaps",IF(H29&lt;=2,"Minor Gaps","Major Gaps - Send Back")))</f>
         <v>Not Reviewed</v>
       </c>
       <c r="J29" s="5"/>
@@ -1199,7 +1322,7 @@
         <v>15</v>
       </c>
       <c r="B34" s="4" t="n">
-        <f aca="false">COUNTIF(I5:I29,"✅ Pass - No Gaps")</f>
+        <f aca="false">COUNTIF(I5:I29,"Pass - No Gaps")</f>
         <v>0</v>
       </c>
     </row>
@@ -1208,7 +1331,7 @@
         <v>16</v>
       </c>
       <c r="B35" s="4" t="n">
-        <f aca="false">COUNTIF(I5:I29,"⚠ Minor Gaps")</f>
+        <f aca="false">COUNTIF(I5:I29,"Minor Gaps")</f>
         <v>0</v>
       </c>
     </row>
@@ -1217,7 +1340,7 @@
         <v>17</v>
       </c>
       <c r="B36" s="4" t="n">
-        <f aca="false">COUNTIF(I5:I29,"❌ Major Gaps - Send Back")</f>
+        <f aca="false">COUNTIF(I5:I29,"Major Gaps - Send Back")</f>
         <v>0</v>
       </c>
     </row>
@@ -1227,9 +1350,21 @@
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A32:B32"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="4">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C5:C29" type="list">
+      <formula1>FaultTypeList</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D5:G29" type="list">
-      <formula1>"Yes,Partial,No"</formula1>
+      <formula1>YesPartialNoList</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J5:J29" type="list">
+      <formula1>NotesPhraseList</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K5:K29" type="list">
+      <formula1>ReviewerList</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -1248,7 +1383,169 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>54</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="110"/>
@@ -1256,12 +1553,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1269,85 +1566,98 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="s">
-        <v>25</v>
-      </c>
+      <c r="A9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
-        <v>26</v>
+      <c r="A10" s="9" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>29</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10"/>
+      <c r="A15" s="10" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="s">
-        <v>31</v>
+      <c r="A16" s="10" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="s">
-        <v>33</v>
-      </c>
+      <c r="A18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>35</v>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="10" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
